--- a/DOSSIES_MULTIFORMATO/BANCO_DAYCOVAL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/BANCO_DAYCOVAL/dossie.xlsx
@@ -469,7 +469,11 @@
           <t>cnpj</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>62.232.889/0001-90</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -503,7 +507,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99481.64</t>
         </is>
       </c>
     </row>
@@ -521,7 +525,11 @@
           <t>faturas_exigiveis</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -529,7 +537,11 @@
           <t>faturas_prescritas</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/DOSSIES_MULTIFORMATO/BANCO_DAYCOVAL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/BANCO_DAYCOVAL/dossie.xlsx
@@ -565,7 +565,11 @@
           <t>data_prescricao_proxima</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2031-04-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
